--- a/Luban/Config/Datas/LevelMap.xlsx
+++ b/Luban/Config/Datas/LevelMap.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:G11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -547,7 +547,175 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>M0 测试棋盘：全开阔（无预置障碍）。参照原版《坚守阵地》——地图本身干净，路径完全由玩家的塔塑造</t>
+          <t>M1 教学：全开阔，无预置障碍；难度 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" t="n">
+        <v>2</v>
+      </c>
+      <c r="C5" t="n">
+        <v>2</v>
+      </c>
+      <c r="D5" t="n">
+        <v>16</v>
+      </c>
+      <c r="E5" t="n">
+        <v>9</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>S...............|................|...##......##...|...##......##...|...##......##...|...##......##...|...##......##...|................|...............E</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>M2 双障碍夹出中段窄口；难度 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" t="n">
+        <v>3</v>
+      </c>
+      <c r="C6" t="n">
+        <v>3</v>
+      </c>
+      <c r="D6" t="n">
+        <v>16</v>
+      </c>
+      <c r="E6" t="n">
+        <v>9</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>S...............|................|....########....|....########....|....########....|................|................|................|...............E</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>M3 厚横墙：好建位变少；难度 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" t="n">
+        <v>4</v>
+      </c>
+      <c r="C7" t="n">
+        <v>4</v>
+      </c>
+      <c r="D7" t="n">
+        <v>16</v>
+      </c>
+      <c r="E7" t="n">
+        <v>9</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>S...............|..#########.....|................|.....#########..|................|..#########.....|................|.....#########..|...............E</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>M4 双交错横墙，S 形走位；难度 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" t="n">
+        <v>5</v>
+      </c>
+      <c r="C8" t="n">
+        <v>5</v>
+      </c>
+      <c r="D8" t="n">
+        <v>16</v>
+      </c>
+      <c r="E8" t="n">
+        <v>9</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>S...............|................|....########....|....########....|....########....|....########....|....########....|................|...............E</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>M5 中央大块障碍，贴路可建位稀缺；难度 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" t="n">
+        <v>6</v>
+      </c>
+      <c r="C9" t="n">
+        <v>6</v>
+      </c>
+      <c r="D9" t="n">
+        <v>16</v>
+      </c>
+      <c r="E9" t="n">
+        <v>9</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>S...............|.##..##..##..##.|.##..##..##..##.|.##..##..##..##.|................|.##..##..##..##.|.##..##..##..##.|.##..##..##..##.|...............E</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>M6 井字街区，内侧位置差；难度 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" t="n">
+        <v>7</v>
+      </c>
+      <c r="C10" t="n">
+        <v>7</v>
+      </c>
+      <c r="D10" t="n">
+        <v>16</v>
+      </c>
+      <c r="E10" t="n">
+        <v>9</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>S...............|.##.##.##.##.##.|.##.##.##.##.##.|.##.##.##.##.##.|................|.##.##.##.##.##.|.##.##.##.##.##.|.##.##.##.##.##.|...............E</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>M7 密集障碍，可建位少、容错低；难度 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" t="n">
+        <v>8</v>
+      </c>
+      <c r="C11" t="n">
+        <v>8</v>
+      </c>
+      <c r="D11" t="n">
+        <v>16</v>
+      </c>
+      <c r="E11" t="n">
+        <v>9</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>S...............|####.##.##.##.##|####.##.##.##.##|................|####.##.##.##.##|####.##.##.##.##|####.##.##.##.##|####.##.##.##.##|...............E</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>M8 终盘：障碍最密，可建位最少；难度 3</t>
         </is>
       </c>
     </row>

--- a/Luban/Config/Datas/LevelMap.xlsx
+++ b/Luban/Config/Datas/LevelMap.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -535,14 +535,14 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="E4" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>S...............|................|................|................|................|................|................|................|...............E</t>
+          <t>...........|...........|S.........E|...........|...........</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">

--- a/Luban/Config/Datas/LevelMap.xlsx
+++ b/Luban/Config/Datas/LevelMap.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:G19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -566,7 +566,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>S...............|................|...##......##...|...##......##...|...##......##...|...##......##...|...##......##...|................|...............E</t>
+          <t>................|................|................|................|S..............E|................|................|................|................</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -583,14 +583,14 @@
         <v>3</v>
       </c>
       <c r="D6" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E6" t="n">
         <v>9</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>S...............|................|....########....|....########....|....########....|................|................|................|...............E</t>
+          <t>........S........|.................|.................|.................|.................|.................|.................|.................|........E........</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -614,7 +614,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>S...............|..#########.....|................|.....#########..|................|..#########.....|................|.....#########..|...............E</t>
+          <t>................|................|................|................|E..............S|................|................|................|................</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -631,14 +631,14 @@
         <v>5</v>
       </c>
       <c r="D8" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E8" t="n">
         <v>9</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>S...............|................|....########....|....########....|....########....|....########....|....########....|................|...............E</t>
+          <t>........E........|.................|.................|.................|.................|.................|.................|.................|........S........</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -662,7 +662,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>S...............|.##..##..##..##.|.##..##..##..##.|.##..##..##..##.|................|.##..##..##..##.|.##..##..##..##.|.##..##..##..##.|...............E</t>
+          <t>S...............|................|................|................|................|................|................|................|...............E</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -686,7 +686,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>S...............|.##.##.##.##.##.|.##.##.##.##.##.|.##.##.##.##.##.|................|.##.##.##.##.##.|.##.##.##.##.##.|.##.##.##.##.##.|...............E</t>
+          <t>S..............E|................|................|................|................|................|................|................|................</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -710,12 +710,204 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>S...............|####.##.##.##.##|####.##.##.##.##|................|####.##.##.##.##|####.##.##.##.##|####.##.##.##.##|####.##.##.##.##|...............E</t>
+          <t>................|................|................|........E.......|................|................|................|................|S...............</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
           <t>M8 终盘：障碍最密，可建位最少；难度 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" t="n">
+        <v>9</v>
+      </c>
+      <c r="C12" t="n">
+        <v>9</v>
+      </c>
+      <c r="D12" t="n">
+        <v>16</v>
+      </c>
+      <c r="E12" t="n">
+        <v>9</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>................|................|................|........E.......|................|................|................|................|...............S</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>M8 终盘：障碍最密，可建位最少；难度 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" t="n">
+        <v>10</v>
+      </c>
+      <c r="C13" t="n">
+        <v>10</v>
+      </c>
+      <c r="D13" t="n">
+        <v>16</v>
+      </c>
+      <c r="E13" t="n">
+        <v>9</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>................|................|S...............|................|................|................|...............E|................|................</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>M1 教学：全开阔，无预置障碍；难度 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" t="n">
+        <v>11</v>
+      </c>
+      <c r="C14" t="n">
+        <v>11</v>
+      </c>
+      <c r="D14" t="n">
+        <v>16</v>
+      </c>
+      <c r="E14" t="n">
+        <v>9</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>S...............|................|................|................|................|................|................|................|E...............</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>M1 教学：全开阔，无预置障碍；难度 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" t="n">
+        <v>12</v>
+      </c>
+      <c r="C15" t="n">
+        <v>12</v>
+      </c>
+      <c r="D15" t="n">
+        <v>16</v>
+      </c>
+      <c r="E15" t="n">
+        <v>9</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>E...............|................|................|................|................|................|................|................|S...............</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>M1 教学：全开阔，无预置障碍；难度 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" t="n">
+        <v>13</v>
+      </c>
+      <c r="C16" t="n">
+        <v>13</v>
+      </c>
+      <c r="D16" t="n">
+        <v>16</v>
+      </c>
+      <c r="E16" t="n">
+        <v>9</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>...............E|................|................|................|................|................|................|................|...............S</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>M1 教学：全开阔，无预置障碍；难度 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" t="n">
+        <v>14</v>
+      </c>
+      <c r="C17" t="n">
+        <v>14</v>
+      </c>
+      <c r="D17" t="n">
+        <v>17</v>
+      </c>
+      <c r="E17" t="n">
+        <v>9</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>.................|.................|.................|........S........|.......###.......|........E........|.................|.................|.................</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>M1 教学：全开阔，无预置障碍；难度 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" t="n">
+        <v>15</v>
+      </c>
+      <c r="C18" t="n">
+        <v>15</v>
+      </c>
+      <c r="D18" t="n">
+        <v>16</v>
+      </c>
+      <c r="E18" t="n">
+        <v>9</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>................|................|................|.......#........|......S#E.......|.......#........|................|................|................</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>M1 教学：全开阔，无预置障碍；难度 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" t="n">
+        <v>16</v>
+      </c>
+      <c r="C19" t="n">
+        <v>16</v>
+      </c>
+      <c r="D19" t="n">
+        <v>16</v>
+      </c>
+      <c r="E19" t="n">
+        <v>9</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>................|................|................|.......#........|S......#.......E|.......#........|................|................|................</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>M1 教学：全开阔，无预置障碍；难度 1</t>
         </is>
       </c>
     </row>

--- a/Luban/Config/Datas/LevelMap.xlsx
+++ b/Luban/Config/Datas/LevelMap.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G19"/>
+  <dimension ref="A1:G23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -911,6 +911,102 @@
         </is>
       </c>
     </row>
+    <row r="20">
+      <c r="B20" t="n">
+        <v>17</v>
+      </c>
+      <c r="C20" t="n">
+        <v>17</v>
+      </c>
+      <c r="D20" t="n">
+        <v>17</v>
+      </c>
+      <c r="E20" t="n">
+        <v>9</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>........S........|.................|.................|.................|.......###.......|.................|.................|.................|........E........</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>M1 教学：全开阔，无预置障碍；难度 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" t="n">
+        <v>18</v>
+      </c>
+      <c r="C21" t="n">
+        <v>18</v>
+      </c>
+      <c r="D21" t="n">
+        <v>16</v>
+      </c>
+      <c r="E21" t="n">
+        <v>9</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>................|................|................|.......#........|E......#.......S|.......#........|................|................|................</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>M1 教学：全开阔，无预置障碍；难度 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" t="n">
+        <v>19</v>
+      </c>
+      <c r="C22" t="n">
+        <v>19</v>
+      </c>
+      <c r="D22" t="n">
+        <v>16</v>
+      </c>
+      <c r="E22" t="n">
+        <v>9</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>S...............|................|................|................|###.............|................|................|................|E...............</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>M1 教学：全开阔，无预置障碍；难度 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" t="n">
+        <v>20</v>
+      </c>
+      <c r="C23" t="n">
+        <v>20</v>
+      </c>
+      <c r="D23" t="n">
+        <v>16</v>
+      </c>
+      <c r="E23" t="n">
+        <v>9</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>................|................|................|................|S#............#E|................|................|................|................</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>M2 双障碍夹出中段窄口；难度 1</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Luban/Config/Datas/LevelMap.xlsx
+++ b/Luban/Config/Datas/LevelMap.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -535,19 +535,19 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E4" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>...........|...........|S.........E|...........|...........</t>
+          <t>.............|.............|.............|S...........E|.............|.............|.............</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>M1 教学：全开阔，无预置障碍；难度 1</t>
+          <t>M1 13x7; obstacles=0; no-build=0; open-route building</t>
         </is>
       </c>
     </row>
@@ -571,7 +571,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>M2 双障碍夹出中段窄口；难度 1</t>
+          <t>M2 16x9; obstacles=0; no-build=0; open-route building</t>
         </is>
       </c>
     </row>
@@ -595,7 +595,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>M3 厚横墙：好建位变少；难度 1</t>
+          <t>M3 17x9; obstacles=0; no-build=0; open-route building</t>
         </is>
       </c>
     </row>
@@ -619,7 +619,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>M4 双交错横墙，S 形走位；难度 2</t>
+          <t>M4 16x9; obstacles=0; no-build=0; open-route building</t>
         </is>
       </c>
     </row>
@@ -643,7 +643,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>M5 中央大块障碍，贴路可建位稀缺；难度 2</t>
+          <t>M5 17x9; obstacles=0; no-build=0; open-route building</t>
         </is>
       </c>
     </row>
@@ -662,12 +662,12 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>S...............|................|................|................|................|................|................|................|...............E</t>
+          <t>S...............|................|.....#..........|.....#..........|................|..........#.....|..........#.....|................|...............E</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>M6 井字街区，内侧位置差；难度 2</t>
+          <t>M6 16x9; obstacles=4; no-build=0; open-route building</t>
         </is>
       </c>
     </row>
@@ -686,12 +686,12 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>S..............E|................|................|................|................|................|................|................|................</t>
+          <t>S..............E|................|.....#..........|.....#..........|................|..........#.....|..........#.....|................|................</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>M7 密集障碍，可建位少、容错低；难度 3</t>
+          <t>M7 16x9; obstacles=4; no-build=0; open-route building</t>
         </is>
       </c>
     </row>
@@ -710,12 +710,12 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>................|................|................|........E.......|................|................|................|................|S...............</t>
+          <t>................|................|.....#..........|.....#..E.......|................|..........#.....|..........#.....|................|S...............</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>M8 终盘：障碍最密，可建位最少；难度 3</t>
+          <t>M8 16x9; obstacles=4; no-build=0; open-route building</t>
         </is>
       </c>
     </row>
@@ -734,12 +734,12 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>................|................|................|........E.......|................|................|................|................|...............S</t>
+          <t>................|................|.....#..........|.....#..E.......|................|..........#.....|..........#.....|................|...............S</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>M8 终盘：障碍最密，可建位最少；难度 3</t>
+          <t>M9 16x9; obstacles=4; no-build=0; open-route building</t>
         </is>
       </c>
     </row>
@@ -758,12 +758,12 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>................|................|S...............|................|................|................|...............E|................|................</t>
+          <t>................|................|S....#..........|.....#..........|................|..........#.....|..........#....E|................|................</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>M1 教学：全开阔，无预置障碍；难度 1</t>
+          <t>M10 16x9; obstacles=4; no-build=0; open-route building</t>
         </is>
       </c>
     </row>
@@ -787,7 +787,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>M1 教学：全开阔，无预置障碍；难度 1</t>
+          <t>M11 16x9; obstacles=0; no-build=0; open-route building</t>
         </is>
       </c>
     </row>
@@ -811,7 +811,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>M1 教学：全开阔，无预置障碍；难度 1</t>
+          <t>M12 16x9; obstacles=0; no-build=0; open-route building</t>
         </is>
       </c>
     </row>
@@ -835,7 +835,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>M1 教学：全开阔，无预置障碍；难度 1</t>
+          <t>M13 16x9; obstacles=0; no-build=0; open-route building</t>
         </is>
       </c>
     </row>
@@ -854,12 +854,12 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>.................|.................|.................|........S........|.......###.......|........E........|.................|.................|.................</t>
+          <t>.................|.................|.................|.................|S......###......E|.................|.................|.................|.................</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>M1 教学：全开阔，无预置障碍；难度 1</t>
+          <t>M14 17x9; obstacles=3; no-build=0; open-route building</t>
         </is>
       </c>
     </row>
@@ -878,12 +878,12 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>................|................|................|.......#........|......S#E.......|.......#........|................|................|................</t>
+          <t>................|................|................|.......#........|S......#.......E|.......#........|................|................|................</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>M1 教学：全开阔，无预置障碍；难度 1</t>
+          <t>M15 16x9; obstacles=3; no-build=0; open-route building</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>M1 教学：全开阔，无预置障碍；难度 1</t>
+          <t>M16 16x9; obstacles=3; no-build=0; open-route building</t>
         </is>
       </c>
     </row>
@@ -931,7 +931,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>M1 教学：全开阔，无预置障碍；难度 1</t>
+          <t>M17 17x9; obstacles=3; no-build=0; open-route building</t>
         </is>
       </c>
     </row>
@@ -955,7 +955,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>M1 教学：全开阔，无预置障碍；难度 1</t>
+          <t>M18 16x9; obstacles=3; no-build=0; open-route building</t>
         </is>
       </c>
     </row>
@@ -979,7 +979,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>M1 教学：全开阔，无预置障碍；难度 1</t>
+          <t>M19 16x9; obstacles=3; no-build=0; open-route building</t>
         </is>
       </c>
     </row>
@@ -1003,7 +1003,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>M2 双障碍夹出中段窄口；难度 1</t>
+          <t>M20 16x9; obstacles=2; no-build=0; open-route building</t>
         </is>
       </c>
     </row>

--- a/Luban/Config/Datas/LevelMap.xlsx
+++ b/Luban/Config/Datas/LevelMap.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G23"/>
+  <dimension ref="A1:G33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1007,6 +1007,246 @@
         </is>
       </c>
     </row>
+    <row r="24">
+      <c r="B24" t="n">
+        <v>21</v>
+      </c>
+      <c r="C24" t="n">
+        <v>21</v>
+      </c>
+      <c r="D24" t="n">
+        <v>17</v>
+      </c>
+      <c r="E24" t="n">
+        <v>9</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>..............#..|S................|................E|.................|.#......#........|.................|.................|...............#.|..#..............</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>M21 17x9; obstacles=5; no-build=0; open-route building</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" t="n">
+        <v>22</v>
+      </c>
+      <c r="C25" t="n">
+        <v>22</v>
+      </c>
+      <c r="D25" t="n">
+        <v>17</v>
+      </c>
+      <c r="E25" t="n">
+        <v>9</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>.................|.................|..#...........#..|.................|.................|.................|................E|S.......#........|...............#.</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>M22 17x9; obstacles=4; no-build=0; open-route building</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" t="n">
+        <v>23</v>
+      </c>
+      <c r="C26" t="n">
+        <v>23</v>
+      </c>
+      <c r="D26" t="n">
+        <v>17</v>
+      </c>
+      <c r="E26" t="n">
+        <v>9</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>.#...............|........#........|S................|................E|.................|.................|.................|...#..........#..|.................</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>M23 17x9; obstacles=4; no-build=0; open-route building</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" t="n">
+        <v>24</v>
+      </c>
+      <c r="C27" t="n">
+        <v>24</v>
+      </c>
+      <c r="D27" t="n">
+        <v>17</v>
+      </c>
+      <c r="E27" t="n">
+        <v>9</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>#................|.................|.................|.#...............|................E|.................|S......#.........|...............#.|..........#......</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>M24 17x9; obstacles=5; no-build=0; open-route building</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="B28" t="n">
+        <v>25</v>
+      </c>
+      <c r="C28" t="n">
+        <v>25</v>
+      </c>
+      <c r="D28" t="n">
+        <v>17</v>
+      </c>
+      <c r="E28" t="n">
+        <v>9</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>.................|..#......#.......|...............#.|S................|.................|................E|.................|.................|..#..............</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>M25 17x9; obstacles=4; no-build=0; open-route building</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" t="n">
+        <v>26</v>
+      </c>
+      <c r="C29" t="n">
+        <v>26</v>
+      </c>
+      <c r="D29" t="n">
+        <v>17</v>
+      </c>
+      <c r="E29" t="n">
+        <v>9</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>#................|....#............|.............#...|.................|.................|S................|................E|.......#.........|...............#.</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>M26 17x9; obstacles=5; no-build=0; open-route building</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="B30" t="n">
+        <v>27</v>
+      </c>
+      <c r="C30" t="n">
+        <v>27</v>
+      </c>
+      <c r="D30" t="n">
+        <v>17</v>
+      </c>
+      <c r="E30" t="n">
+        <v>9</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>...............#.|S........#.......|.................|................E|.................|.................|.................|..#...........#..|.................</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>M27 17x9; obstacles=4; no-build=0; open-route building</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="B31" t="n">
+        <v>28</v>
+      </c>
+      <c r="C31" t="n">
+        <v>28</v>
+      </c>
+      <c r="D31" t="n">
+        <v>17</v>
+      </c>
+      <c r="E31" t="n">
+        <v>9</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>#................|................E|.................|.................|..#............#.|.................|.................|S................|.........#.......</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>M28 17x9; obstacles=4; no-build=0; open-route building</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="B32" t="n">
+        <v>29</v>
+      </c>
+      <c r="C32" t="n">
+        <v>29</v>
+      </c>
+      <c r="D32" t="n">
+        <v>17</v>
+      </c>
+      <c r="E32" t="n">
+        <v>9</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>.................|.................|..............#..|.................|S................|.................|................E|.#.....#.........|...............#.</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>M29 17x9; obstacles=4; no-build=0; open-route building</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="B33" t="n">
+        <v>30</v>
+      </c>
+      <c r="C33" t="n">
+        <v>30</v>
+      </c>
+      <c r="D33" t="n">
+        <v>17</v>
+      </c>
+      <c r="E33" t="n">
+        <v>9</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>.#...............|.................|S..........#.....|.................|.................|................E|..#..............|.................|...............#.</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>M30 17x9; obstacles=4; no-build=0; open-route building</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Luban/Config/Datas/LevelMap.xlsx
+++ b/Luban/Config/Datas/LevelMap.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -710,7 +710,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>................|................|.....#..........|.....#..E.......|................|..........#.....|..........#.....|................|S...............</t>
+          <t>................|................|.....#..........|.....#.........E|................|..........#.....|..........#.....|................|S...............</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -734,7 +734,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>................|................|.....#..........|.....#..E.......|................|..........#.....|..........#.....|................|...............S</t>
+          <t>................|................|.....#..........|E....#..........|................|..........#.....|..........#.....|................|...............S</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -830,7 +830,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>...............E|................|................|................|................|................|................|................|...............S</t>
+          <t>E...............|................|................|................|................|................|................|................|...............S</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -974,7 +974,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>S...............|................|................|................|###.............|................|................|................|E...............</t>
+          <t>S...............|................|................|................|###.............|................|................|................|...............E</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -1142,7 +1142,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>#................|....#............|.............#...|.................|.................|S................|................E|.......#.........|...............#.</t>
+          <t>#.......S........|....#............|.............#...|.................|.................|.................|.................|.......#.........|........E......#.</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
